--- a/db/templates/delivery_default.xlsx
+++ b/db/templates/delivery_default.xlsx
@@ -29,7 +29,7 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>VAT: {{organization.vatin}}</t>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
   </si>
   <si>
     <t>{{organization.email}} | {{organization.phone}}</t>

--- a/db/templates/delivery_default.xlsx
+++ b/db/templates/delivery_default.xlsx
@@ -7,18 +7,21 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Delivery Note" sheetId="1" r:id="rId1"/>
+    <sheet name="Bon de livraison" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Delivery Note'!$1:$13</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Bon de livraison'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+  <si>
+    <t>{{organization.logo}}</t>
+  </si>
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -29,28 +32,10 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{organization.email}} | {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>DELIVERY NOTE</t>
-  </si>
-  <si>
-    <t>Delivery number: {{delivery.number}}</t>
-  </si>
-  <si>
-    <t>Delivery date: {{delivery.date}}</t>
-  </si>
-  <si>
-    <t>Order: {{delivery.orderNumber}}</t>
-  </si>
-  <si>
-    <t>Tracking number: {{delivery.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Deliver To</t>
+    <t>Tél : {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>MF : {{organization.vatin}}</t>
   </si>
   <si>
     <t>{{client.name}}</t>
@@ -62,193 +47,250 @@
     <t>{{client.postalCode}} {{client.city}}</t>
   </si>
   <si>
-    <t>Shipping address: {{delivery.shippingAddress}}</t>
+    <t>Tel: {{client.phone}}</t>
+  </si>
+  <si>
+    <t>CIN: {{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Bon de livraison N°: {{delivery.number}}</t>
+  </si>
+  <si>
+    <t>Date : {{delivery.date}}</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>Unité</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unit}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Cachet et Signature</t>
+  </si>
+  <si>
+    <t>IBAN : {{organization.iban}}</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{delivery.number}}</t>
+  </si>
+  <si>
+    <t>Delivery number</t>
+  </si>
+  <si>
+    <t>{{delivery.date}}</t>
+  </si>
+  <si>
+    <t>Delivery date</t>
+  </si>
+  <si>
+    <t>{{delivery.orderNumber}}</t>
+  </si>
+  <si>
+    <t>Linked order number, blank on a standalone delivery</t>
+  </si>
+  <si>
+    <t>{{delivery.shippingAddress}}</t>
+  </si>
+  <si>
+    <t>Free-text shipping address, blank if unset</t>
+  </si>
+  <si>
+    <t>{{delivery.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number, blank if unset</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Seller IBAN</t>
+  </si>
+  <si>
+    <t>Seller bank name</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT number</t>
+  </si>
+  <si>
+    <t>{{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Customer national ID / CIN number</t>
+  </si>
+  <si>
+    <t>{{client.address}}</t>
+  </si>
+  <si>
+    <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>{{client.email}}</t>
+  </si>
+  <si>
+    <t>Customer email</t>
+  </si>
+  <si>
+    <t>{{client.phone}}</t>
+  </si>
+  <si>
+    <t>Customer phone</t>
+  </si>
+  <si>
+    <t>{{client.phone2}}</t>
+  </si>
+  <si>
+    <t>Customer phone 2</t>
+  </si>
+  <si>
+    <t>{{client.phone3}}</t>
+  </si>
+  <si>
+    <t>Customer phone 3</t>
+  </si>
+  <si>
+    <t>{{client.street}}</t>
+  </si>
+  <si>
+    <t>Customer street</t>
+  </si>
+  <si>
+    <t>{{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Customer house number</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}}</t>
+  </si>
+  <si>
+    <t>Customer postal code</t>
+  </si>
+  <si>
+    <t>{{client.city}}</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Linked product's SKU</t>
+  </si>
+  <si>
+    <t>Line item description</t>
   </si>
   <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}} {{lineItems.unit}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Notes: {{delivery.notes}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>{{delivery.number}}</t>
-  </si>
-  <si>
-    <t>Delivery number</t>
-  </si>
-  <si>
-    <t>{{delivery.date}}</t>
-  </si>
-  <si>
-    <t>Delivery date</t>
-  </si>
-  <si>
-    <t>{{delivery.orderNumber}}</t>
-  </si>
-  <si>
-    <t>Linked sales order number, blank if standalone</t>
-  </si>
-  <si>
-    <t>{{delivery.shippingAddress}}</t>
-  </si>
-  <si>
-    <t>Free-text shipping address, blank if unset</t>
-  </si>
-  <si>
-    <t>{{delivery.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Carrier tracking number, blank if unset</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>Customer name, blank on a walk-in/no-client delivery</t>
-  </si>
-  <si>
-    <t>{{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Customer VAT number</t>
-  </si>
-  <si>
-    <t>{{client.email}}</t>
-  </si>
-  <si>
-    <t>Customer email</t>
-  </si>
-  <si>
-    <t>{{client.phone}}</t>
-  </si>
-  <si>
-    <t>Customer phone</t>
-  </si>
-  <si>
-    <t>{{client.street}}</t>
-  </si>
-  <si>
-    <t>Customer street</t>
-  </si>
-  <si>
-    <t>{{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Customer house number</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}}</t>
-  </si>
-  <si>
-    <t>Customer postal code</t>
-  </si>
-  <si>
-    <t>{{client.city}}</t>
-  </si>
-  <si>
-    <t>Customer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>Linked product's SKU, blank on a free-text line or an unset SKU</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unit}}</t>
-  </si>
-  <si>
-    <t>Unit of measure (e.g. pcs, kg), blank if unset</t>
+    <t>Unit of measure, blank if unset</t>
   </si>
   <si>
     <t>Footer</t>
@@ -266,7 +308,7 @@
     <t>{{export.generatedDate}}</t>
   </si>
   <si>
-    <t>Date this file was exported (not the delivery's own date), in the organization's date format</t>
+    <t>Date this file was exported, in the organization's date format</t>
   </si>
   <si>
     <t>{{export.generatedTime}}</t>
@@ -278,14 +320,14 @@
     <t>&amp;P (page number) / &amp;N (total pages)</t>
   </si>
   <si>
-    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
+    <t>Native Excel/LibreOffice codes, only work in Page Layout ▸ Header/Footer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -306,13 +348,19 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
       <color/>
       <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
@@ -329,16 +377,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -346,11 +394,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -358,22 +420,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -649,112 +723,149 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="24"/>
-    <col customWidth="true" max="2" min="2" width="16"/>
-    <col customWidth="true" max="3" min="3" width="22"/>
-    <col customWidth="true" max="4" min="4" width="16"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="34"/>
+    <col customWidth="true" max="4" min="3" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
+      <c r="A7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="B12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="J12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="D18" s="8" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
+  <mergeCells count="10">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:G22"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -774,301 +885,357 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>23</v>
+      <c r="A1" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>24</v>
+      <c r="A2" s="12" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>15</v>
+      <c r="A4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>27</v>
+      <c r="A5" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="s">
-        <v>70</v>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="s">
-        <v>77</v>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
+      <c r="A35" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
-        <v>80</v>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/delivery_default.xlsx
+++ b/db/templates/delivery_default.xlsx
@@ -7,11 +7,11 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Bon de livraison" sheetId="1" r:id="rId1"/>
+    <sheet name="Delivery Note" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Bon de livraison'!$1:$11</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Delivery Note'!$1:$13</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -20,274 +20,274 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>{{organization.email}} | {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>DELIVERY NOTE</t>
+  </si>
+  <si>
+    <t>Delivery number: {{delivery.number}}</t>
+  </si>
+  <si>
+    <t>Delivery date: {{delivery.date}}</t>
+  </si>
+  <si>
+    <t>Order: {{delivery.orderNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number: {{delivery.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Deliver To</t>
+  </si>
+  <si>
+    <t>{{client.name}}</t>
+  </si>
+  <si>
+    <t>{{client.street}} {{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}} {{client.city}}</t>
+  </si>
+  <si>
+    <t>Shipping address: {{delivery.shippingAddress}}</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}} {{lineItems.unit}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Notes: {{delivery.notes}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
     <t>{{organization.logo}}</t>
   </si>
   <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Tél : {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>MF : {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{client.name}}</t>
-  </si>
-  <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}} {{client.city}}</t>
-  </si>
-  <si>
-    <t>Tel: {{client.phone}}</t>
-  </si>
-  <si>
-    <t>CIN: {{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Bon de livraison N°: {{delivery.number}}</t>
-  </si>
-  <si>
-    <t>Date : {{delivery.date}}</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Désignation</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>Unité</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{delivery.number}}</t>
+  </si>
+  <si>
+    <t>Delivery number</t>
+  </si>
+  <si>
+    <t>{{delivery.date}}</t>
+  </si>
+  <si>
+    <t>Delivery date</t>
+  </si>
+  <si>
+    <t>{{delivery.orderNumber}}</t>
+  </si>
+  <si>
+    <t>Linked order number, blank on a standalone delivery</t>
+  </si>
+  <si>
+    <t>{{delivery.shippingAddress}}</t>
+  </si>
+  <si>
+    <t>Free-text shipping address, blank if unset</t>
+  </si>
+  <si>
+    <t>{{delivery.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number, blank if unset</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Seller IBAN</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Seller bank name</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT number</t>
+  </si>
+  <si>
+    <t>{{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Customer national ID / CIN number</t>
+  </si>
+  <si>
+    <t>{{client.address}}</t>
+  </si>
+  <si>
+    <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>{{client.email}}</t>
+  </si>
+  <si>
+    <t>Customer email</t>
+  </si>
+  <si>
+    <t>{{client.phone}}</t>
+  </si>
+  <si>
+    <t>Customer phone</t>
+  </si>
+  <si>
+    <t>{{client.phone2}}</t>
+  </si>
+  <si>
+    <t>Customer phone 2</t>
+  </si>
+  <si>
+    <t>{{client.phone3}}</t>
+  </si>
+  <si>
+    <t>Customer phone 3</t>
+  </si>
+  <si>
+    <t>{{client.street}}</t>
+  </si>
+  <si>
+    <t>Customer street</t>
+  </si>
+  <si>
+    <t>{{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Customer house number</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}}</t>
+  </si>
+  <si>
+    <t>Customer postal code</t>
+  </si>
+  <si>
+    <t>{{client.city}}</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Linked product's SKU</t>
+  </si>
+  <si>
+    <t>Line item description</t>
   </si>
   <si>
     <t>{{lineItems.quantity}}</t>
   </si>
   <si>
     <t>{{lineItems.unit}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Cachet et Signature</t>
-  </si>
-  <si>
-    <t>IBAN : {{organization.iban}}</t>
-  </si>
-  <si>
-    <t>{{organization.bankName}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Seller logo — place alone in a cell to anchor the uploaded image there</t>
-  </si>
-  <si>
-    <t>{{delivery.number}}</t>
-  </si>
-  <si>
-    <t>Delivery number</t>
-  </si>
-  <si>
-    <t>{{delivery.date}}</t>
-  </si>
-  <si>
-    <t>Delivery date</t>
-  </si>
-  <si>
-    <t>{{delivery.orderNumber}}</t>
-  </si>
-  <si>
-    <t>Linked order number, blank on a standalone delivery</t>
-  </si>
-  <si>
-    <t>{{delivery.shippingAddress}}</t>
-  </si>
-  <si>
-    <t>Free-text shipping address, blank if unset</t>
-  </si>
-  <si>
-    <t>{{delivery.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Tracking number, blank if unset</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>{{organization.iban}}</t>
-  </si>
-  <si>
-    <t>Seller IBAN</t>
-  </si>
-  <si>
-    <t>Seller bank name</t>
-  </si>
-  <si>
-    <t>Customer name</t>
-  </si>
-  <si>
-    <t>{{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Customer VAT number</t>
-  </si>
-  <si>
-    <t>{{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Customer national ID / CIN number</t>
-  </si>
-  <si>
-    <t>{{client.address}}</t>
-  </si>
-  <si>
-    <t>Customer single-line address</t>
-  </si>
-  <si>
-    <t>{{client.email}}</t>
-  </si>
-  <si>
-    <t>Customer email</t>
-  </si>
-  <si>
-    <t>{{client.phone}}</t>
-  </si>
-  <si>
-    <t>Customer phone</t>
-  </si>
-  <si>
-    <t>{{client.phone2}}</t>
-  </si>
-  <si>
-    <t>Customer phone 2</t>
-  </si>
-  <si>
-    <t>{{client.phone3}}</t>
-  </si>
-  <si>
-    <t>Customer phone 3</t>
-  </si>
-  <si>
-    <t>{{client.street}}</t>
-  </si>
-  <si>
-    <t>Customer street</t>
-  </si>
-  <si>
-    <t>{{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Customer house number</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}}</t>
-  </si>
-  <si>
-    <t>Customer postal code</t>
-  </si>
-  <si>
-    <t>{{client.city}}</t>
-  </si>
-  <si>
-    <t>Customer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
-  </si>
-  <si>
-    <t>Linked product's SKU</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>Quantity</t>
   </si>
   <si>
     <t>Unit of measure, blank if unset</t>
@@ -354,13 +354,13 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="14"/>
     </font>
     <font>
       <family val="2"/>
@@ -412,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -438,10 +438,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -723,149 +726,112 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="34"/>
-    <col customWidth="true" max="4" min="3" width="16"/>
+    <col customWidth="true" max="1" min="1" width="24"/>
+    <col customWidth="true" max="2" min="2" width="16"/>
+    <col customWidth="true" max="3" min="3" width="22"/>
+    <col customWidth="true" max="4" min="4" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J12" t="s">
+      <c r="E14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="8" t="s">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:G22"/>
+  <mergeCells count="2">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -885,266 +851,266 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="C4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
         <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
         <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
         <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
         <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
         <v>75</v>
-      </c>
-      <c r="C30" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
         <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
         <v>79</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" t="s">
         <v>83</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="36">
@@ -1152,15 +1118,15 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38">
@@ -1168,27 +1134,27 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1201,7 +1167,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>94</v>
       </c>
     </row>

--- a/db/templates/delivery_default.xlsx
+++ b/db/templates/delivery_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -56,7 +56,7 @@
     <t>{{client.name}}</t>
   </si>
   <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
+    <t>{{client.addressLine}}</t>
   </si>
   <si>
     <t>{{client.postalCode}} {{client.city}}</t>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>Customer street and house number, or the single-line address when there is no street</t>
   </si>
   <si>
     <t>{{client.email}}</t>
@@ -1046,84 +1049,84 @@
     </row>
     <row r="27">
       <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
         <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
         <v>70</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
         <v>72</v>
-      </c>
-      <c r="C29" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
         <v>74</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
         <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" t="s">
         <v>78</v>
-      </c>
-      <c r="C32" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
         <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
         <v>82</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35">
+      <c r="B35" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="s">
+      <c r="C35" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="A36" s="12" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
         <v>86</v>
@@ -1131,7 +1134,7 @@
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" t="s">
         <v>87</v>
@@ -1139,10 +1142,10 @@
     </row>
     <row r="39">
       <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
         <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -1150,58 +1153,66 @@
         <v>89</v>
       </c>
       <c r="C40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="s">
+      <c r="C41" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="s">
+      <c r="A42" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43">
+      <c r="B43" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="s">
+      <c r="C43" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="s">
+      <c r="A44" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s">
         <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
         <v>99</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47">
+      <c r="B47" t="s">
         <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
 </worksheet>
 </file>